--- a/artfynd/A 52841-2025 artfynd.xlsx
+++ b/artfynd/A 52841-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,6 +1518,128 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96463923</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kållebäck, sumpskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527378.3420991394</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6353496.505303426</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ett bestånd med 10-tal skott i V. slänten</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52841-2025 artfynd.xlsx
+++ b/artfynd/A 52841-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74963369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73648022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80631989</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Kalkbarrsvampar 2018</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73648092</t>
         </is>
       </c>
     </row>
@@ -1195,6 +1220,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73648011</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,8 +1330,21 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73648021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>